--- a/ReconAI_Backend_Security_Review_Report.xlsx
+++ b/ReconAI_Backend_Security_Review_Report.xlsx
@@ -59,7 +59,7 @@
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>2026-08-02</t>
+    <t>2026-08-06</t>
   </si>
   <si>
     <t>Compliance:</t>
